--- a/terminology/CodeSystem-v2-0131-cz.xlsx
+++ b/terminology/CodeSystem-v2-0131-cz.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -133,16 +133,19 @@
     <t>Type</t>
   </si>
   <si>
-    <t>notSelectable</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#notSelectable</t>
-  </si>
-  <si>
-    <t>Not Selectable</t>
-  </si>
-  <si>
-    <t>boolean</t>
+    <t>preferredForLanguage</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>code</t>
   </si>
   <si>
     <t>Level</t>
@@ -534,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -555,14 +558,24 @@
       <c r="A2" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="C2" t="s" s="2">
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="B3" t="s" s="2">
         <v>42</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -577,128 +590,128 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
